--- a/content_forms/008_podcast_audio_submission_upload_form--content_forms.xlsx
+++ b/content_forms/008_podcast_audio_submission_upload_form--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'everyone'}</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Everyone'}</t>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'hosts'}</t>
+          <t>hosts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Hosts'}</t>
+          <t>Hosts</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'everyone'}</t>
+          <t>everyone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Everyone'}</t>
+          <t>Everyone</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'team'}</t>
+          <t>team</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Team'}</t>
+          <t>Team</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'hosts'}</t>
+          <t>hosts</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Hosts'}</t>
+          <t>Hosts</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'new_tab'}</t>
+          <t>new_tab</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'New Tab'}</t>
+          <t>New Tab</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'current_tab'}</t>
+          <t>current_tab</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Current Tab'}</t>
+          <t>Current Tab</t>
         </is>
       </c>
     </row>
